--- a/src/result/lfw/comparison_no_svd.xlsx
+++ b/src/result/lfw/comparison_no_svd.xlsx
@@ -413,100 +413,85 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1_score</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0.5934718100890207</v>
       </c>
       <c r="B2" t="n">
+        <v>0.5922732140537652</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.5934718100890207</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.5922732140537652</v>
-      </c>
       <c r="D2" t="n">
-        <v>0.5934718100890207</v>
+        <v>0.5906855625219409</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5906855625219409</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.689130783081055</v>
+        <v>2.848417997360229</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SVM Linear</t>
-        </is>
+      <c r="A3" t="n">
+        <v>0.8249258160237388</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8219584569732937</v>
+        <v>0.8324778137486987</v>
       </c>
       <c r="C3" t="n">
-        <v>0.827122715027623</v>
+        <v>0.8249258160237388</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8219584569732937</v>
+        <v>0.82633665194647</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8215744541922088</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.325953483581543</v>
+        <v>1.474628210067749</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SVM RBF</t>
-        </is>
+      <c r="A4" t="n">
+        <v>0.8219584569732937</v>
       </c>
       <c r="B4" t="n">
+        <v>0.8259121596973571</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.8219584569732937</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.8259121596973571</v>
-      </c>
       <c r="D4" t="n">
-        <v>0.8219584569732937</v>
+        <v>0.8176635612896228</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8176635612896228</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.819473743438721</v>
+        <v>3.06232476234436</v>
       </c>
     </row>
   </sheetData>

--- a/src/result/lfw/comparison_no_svd.xlsx
+++ b/src/result/lfw/comparison_no_svd.xlsx
@@ -457,7 +457,7 @@
         <v>0.5906855625219409</v>
       </c>
       <c r="E2" t="n">
-        <v>2.848417997360229</v>
+        <v>1.672689199447632</v>
       </c>
     </row>
     <row r="3">
@@ -474,7 +474,7 @@
         <v>0.82633665194647</v>
       </c>
       <c r="E3" t="n">
-        <v>1.474628210067749</v>
+        <v>1.400212287902832</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>0.8176635612896228</v>
       </c>
       <c r="E4" t="n">
-        <v>3.06232476234436</v>
+        <v>3.069623708724976</v>
       </c>
     </row>
   </sheetData>
